--- a/UserScore/thoughts.xlsx
+++ b/UserScore/thoughts.xlsx
@@ -639,7 +639,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -650,13 +650,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1124,148 +1117,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1654,9 +1647,7 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
+      <c r="D2"/>
       <c r="E2" t="s">
         <v>7</v>
       </c>
@@ -1671,9 +1662,7 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
+      <c r="D3"/>
       <c r="E3" t="s">
         <v>7</v>
       </c>
@@ -1688,9 +1677,7 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
+      <c r="D4"/>
       <c r="E4" t="s">
         <v>7</v>
       </c>
@@ -1705,12 +1692,8 @@
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>46097</v>
-      </c>
+      <c r="D5"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">

--- a/UserScore/thoughts.xlsx
+++ b/UserScore/thoughts.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,8 +492,14 @@
           <t>Immanuel Kant</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">

--- a/UserScore/thoughts.xlsx
+++ b/UserScore/thoughts.xlsx
@@ -515,8 +515,14 @@
           <t>Marcus Aurelius</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,8 +538,14 @@
           <t>Albert Einstein</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,8 +561,14 @@
           <t>Charles Darwin</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,8 +584,14 @@
           <t>Lord Acton</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">

--- a/UserScore/thoughts.xlsx
+++ b/UserScore/thoughts.xlsx
@@ -607,8 +607,14 @@
           <t>Friedrich Nietzsche</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">

--- a/UserScore/thoughts.xlsx
+++ b/UserScore/thoughts.xlsx
@@ -630,8 +630,14 @@
           <t>Ambrose Redmoon</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -647,8 +653,14 @@
           <t>Viktor Frankl</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -664,8 +676,14 @@
           <t>Friedrich Nietzsche</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -681,8 +699,14 @@
           <t>Søren Kierkegaard</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -698,8 +722,14 @@
           <t>Aristotle</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -715,8 +745,14 @@
           <t>Edward Young</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
